--- a/Child nutrition - FMOH Use Case Prioritization Criteria.xlsx
+++ b/Child nutrition - FMOH Use Case Prioritization Criteria.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/Haramaya University</t>
+    <t xml:space="preserve">MoH/Haramaya University</t>
   </si>
   <si>
     <t xml:space="preserve">Child nutrition</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Malnutrition - identify regions at risk of acute malnutrition to support early detection</t>
   </si>
   <si>
-    <t xml:space="preserve">How can early warning and rapid detection of acute malnutrition be strengthened in drought‑prone  Ethiopia?</t>
+    <t xml:space="preserve">1. How can early warning and rapid detection of acute malnutrition be strengthened in drought‑prone Ethiopia?</t>
   </si>
   <si>
     <t xml:space="preserve">no</t>
@@ -85,13 +85,13 @@
     <t xml:space="preserve">universities, Nutrition office (Ministry of Health), Lead executive office, Ministry of Agriculture</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/Nutrition office</t>
+    <t xml:space="preserve">MoH/Nutrition office</t>
   </si>
   <si>
     <t xml:space="preserve">Child growth - identify risk factors for poor growth outcomes</t>
   </si>
   <si>
-    <t xml:space="preserve">What factors are associated with poor growth outcomes in children under 2?</t>
+    <t xml:space="preserve">1. What factors are associated with poor growth outcomes in children under 2?</t>
   </si>
   <si>
     <t xml:space="preserve">1: lack of individual-level data, 2: many risk factors are already known, which limits the impact, 3: may be difficult to change policy as a result of results</t>
@@ -176,9 +176,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -241,7 +240,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,6 +271,10 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -612,7 +615,7 @@
       <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="1" t="n">
@@ -651,7 +654,7 @@
       <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="1" t="n">
